--- a/isms-core-framework/A.5-organizational-controls/isms-a.5.24-28-incident-management-lifecycle/WKBK/90_workbooks/ISMS-IMP-A.5.24-28.S1_Framework_Assessment_20260208.xlsx
+++ b/isms-core-framework/A.5-organizational-controls/isms-a.5.24-28-incident-management-lifecycle/WKBK/90_workbooks/ISMS-IMP-A.5.24-28.S1_Framework_Assessment_20260208.xlsx
@@ -1615,7 +1615,7 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>(If PCI DSS applies) Is PCI DSS incident reporting procedure documented?</t>
+          <t>(If PCI DSS v4.0.1 applies) Is PCI DSS v4.0.1 incident reporting procedure documented?</t>
         </is>
       </c>
       <c r="D23" s="5" t="n"/>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>Are drills conducted specifically for regulatory breach notification (GDPR 72-hour, PCI DSS, etc.)?</t>
+          <t>Are drills conducted specifically for regulatory breach notification (GDPR 72-hour, PCI DSS v4.0.1, etc.)?</t>
         </is>
       </c>
       <c r="D17" s="5" t="n"/>
